--- a/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_ΡΟΗ_ΜΟΝΟΠΡΟΣΩΠΗ_ΙΚΕ_2026-02.xlsx
+++ b/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_ΡΟΗ_ΜΟΝΟΠΡΟΣΩΠΗ_ΙΚΕ_2026-02.xlsx
@@ -2844,7 +2844,7 @@
     <row r="6" ht="60.75" customFormat="1" customHeight="1" s="10">
       <c r="B6" s="80" t="inlineStr">
         <is>
-          <t>06/03/26</t>
+          <t>09/03/26</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -3196,13 +3196,13 @@
         <v>2071.48</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>0</v>
+        <v>48.2932376</v>
       </c>
       <c r="F23" s="25" t="n">
         <v>2.07</v>
       </c>
       <c r="G23" s="92" t="n">
-        <v>0</v>
+        <v>23.31</v>
       </c>
       <c r="H23" s="93" t="n"/>
     </row>
@@ -3236,13 +3236,13 @@
         <v>1551.2</v>
       </c>
       <c r="E25" s="25" t="n">
-        <v>0</v>
+        <v>15.9627054</v>
       </c>
       <c r="F25" s="25" t="n">
         <v>1.55</v>
       </c>
       <c r="G25" s="92" t="n">
-        <v>0</v>
+        <v>10.29</v>
       </c>
       <c r="H25" s="93" t="n"/>
     </row>
@@ -3416,13 +3416,13 @@
         <v>907.96</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>0</v>
+        <v>4.7933892</v>
       </c>
       <c r="F34" s="25" t="n">
         <v>0.91</v>
       </c>
       <c r="G34" s="92" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="H34" s="93" t="n"/>
     </row>
@@ -3436,13 +3436,13 @@
         <v>1031.46</v>
       </c>
       <c r="E35" s="25" t="n">
-        <v>16.376561</v>
+        <v>14.5213106</v>
       </c>
       <c r="F35" s="25" t="n">
         <v>1.03</v>
       </c>
       <c r="G35" s="92" t="n">
-        <v>15.88</v>
+        <v>14.08</v>
       </c>
       <c r="H35" s="93" t="n"/>
     </row>
@@ -3456,13 +3456,13 @@
         <v>2664.74</v>
       </c>
       <c r="E36" s="25" t="n">
-        <v>0</v>
+        <v>37.9186018</v>
       </c>
       <c r="F36" s="25" t="n">
         <v>2.66</v>
       </c>
       <c r="G36" s="92" t="n">
-        <v>0</v>
+        <v>14.23</v>
       </c>
       <c r="H36" s="93" t="n"/>
     </row>
@@ -3476,13 +3476,13 @@
         <v>477.4</v>
       </c>
       <c r="E37" s="25" t="n">
-        <v>0</v>
+        <v>2.9516796</v>
       </c>
       <c r="F37" s="25" t="n">
         <v>0.48</v>
       </c>
       <c r="G37" s="92" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="H37" s="93" t="n"/>
     </row>
@@ -3496,13 +3496,13 @@
         <v>36250.78</v>
       </c>
       <c r="E38" s="95" t="n">
-        <v>1568.55</v>
+        <v>1676.62</v>
       </c>
       <c r="F38" s="95" t="n">
         <v>36.24</v>
       </c>
       <c r="G38" s="96" t="n">
-        <v>43.27</v>
+        <v>46.25</v>
       </c>
       <c r="H38" s="93" t="n"/>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="G46" s="83" t="n"/>
       <c r="H46" s="105" t="n">
-        <v>1568.55</v>
+        <v>1676.62</v>
       </c>
       <c r="I46" s="45" t="n"/>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="C53" s="110" t="inlineStr">
         <is>
-          <t>08/03/26</t>
+          <t>11/03/26</t>
         </is>
       </c>
       <c r="D53" s="111" t="n"/>
